--- a/02_Zero_Shot/outputs/NLI/Cross-Encoder DeBERTa/RESULT_f-droid_cross-encoder-deberta_zeroshot.xlsx
+++ b/02_Zero_Shot/outputs/NLI/Cross-Encoder DeBERTa/RESULT_f-droid_cross-encoder-deberta_zeroshot.xlsx
@@ -48836,7 +48836,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>94.22418119400027</v>
+        <v>114.447194098997</v>
       </c>
     </row>
     <row r="8">
@@ -48846,7 +48846,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03316585047307295</v>
+        <v>0.04028412323090355</v>
       </c>
     </row>
   </sheetData>
